--- a/raw/biometrico/ENERO-2026.xlsx
+++ b/raw/biometrico/ENERO-2026.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ventap06\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JosueLopezDeLaTorre\Documents\source\talento\raw\biometrico\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB1E4491-68AF-4AFF-A2C0-6F2091D37779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8171B895-9956-4986-AEE5-166BBF8C4687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3765" yWindow="1005" windowWidth="22710" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
-    <sheet name="REPORTE BH" sheetId="12" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$B$1:$B$4583</definedName>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2900" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2886" uniqueCount="39">
   <si>
     <t>Número</t>
   </si>
@@ -147,48 +146,6 @@
   <si>
     <t>LILI ANDRADE ANDRADE</t>
   </si>
-  <si>
-    <t>ALMUERZO</t>
-  </si>
-  <si>
-    <t>DESAYUNO</t>
-  </si>
-  <si>
-    <t>HORARIOS</t>
-  </si>
-  <si>
-    <t>MADRUGADA</t>
-  </si>
-  <si>
-    <t>SALIDA</t>
-  </si>
-  <si>
-    <t>ORDINARIO</t>
-  </si>
-  <si>
-    <t>INVENTARIO</t>
-  </si>
-  <si>
-    <t>TURNOS</t>
-  </si>
-  <si>
-    <t>ENTRADA</t>
-  </si>
-  <si>
-    <t>ALIMENTACION</t>
-  </si>
-  <si>
-    <t>15 MINUTOS</t>
-  </si>
-  <si>
-    <t>30 MINUTOS</t>
-  </si>
-  <si>
-    <t>TODOS TIENEN UN DÍA LIBRE A LA SEMANA</t>
-  </si>
-  <si>
-    <t>DOMINGOS</t>
-  </si>
 </sst>
 </file>
 
@@ -198,7 +155,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="d/m/yyyy\ h:mm:ss"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -214,40 +171,6 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -270,7 +193,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -293,26 +216,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -326,34 +234,6 @@
     </xf>
     <xf numFmtId="165" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -40795,166 +40675,4 @@
   <autoFilter ref="B1:B4583" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:L42"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="15.140625" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" customWidth="1"/>
-    <col min="6" max="6" width="7.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="8">
-        <v>0.22916666666666666</v>
-      </c>
-      <c r="C3" s="8">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G3" s="9"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="8">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.75</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="G4" s="9"/>
-    </row>
-    <row r="5" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="8">
-        <v>0.375</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" s="17">
-        <v>0.25</v>
-      </c>
-      <c r="C6" s="17">
-        <v>0.58333333333333337</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-    </row>
-    <row r="8" spans="1:12" ht="12.75" x14ac:dyDescent="0.2"/>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2"/>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2"/>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2"/>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2"/>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2"/>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2"/>
-    <row r="17" x14ac:dyDescent="0.2"/>
-    <row r="18" x14ac:dyDescent="0.2"/>
-    <row r="19" x14ac:dyDescent="0.2"/>
-    <row r="20" x14ac:dyDescent="0.2"/>
-    <row r="21" x14ac:dyDescent="0.2"/>
-    <row r="22" x14ac:dyDescent="0.2"/>
-    <row r="23" x14ac:dyDescent="0.2"/>
-    <row r="24" x14ac:dyDescent="0.2"/>
-    <row r="25" x14ac:dyDescent="0.2"/>
-    <row r="26" x14ac:dyDescent="0.2"/>
-    <row r="27" x14ac:dyDescent="0.2"/>
-    <row r="28" x14ac:dyDescent="0.2"/>
-    <row r="29" x14ac:dyDescent="0.2"/>
-    <row r="30" x14ac:dyDescent="0.2"/>
-    <row r="31" x14ac:dyDescent="0.2"/>
-    <row r="32" x14ac:dyDescent="0.2"/>
-    <row r="33" x14ac:dyDescent="0.2"/>
-    <row r="34" x14ac:dyDescent="0.2"/>
-    <row r="35" x14ac:dyDescent="0.2"/>
-    <row r="36" x14ac:dyDescent="0.2"/>
-    <row r="37" x14ac:dyDescent="0.2"/>
-    <row r="38" x14ac:dyDescent="0.2"/>
-    <row r="39" x14ac:dyDescent="0.2"/>
-    <row r="40" x14ac:dyDescent="0.2"/>
-    <row r="41" x14ac:dyDescent="0.2"/>
-    <row r="42" x14ac:dyDescent="0.2"/>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="A7:G7"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>